--- a/artfynd/A 34803-2026 artfynd.xlsx
+++ b/artfynd/A 34803-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145878</v>
       </c>
       <c r="B2" t="n">
-        <v>92015</v>
+        <v>92016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145849</v>
       </c>
       <c r="B3" t="n">
-        <v>92460</v>
+        <v>92461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136145813</v>
       </c>
       <c r="B16" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136145835</v>
       </c>
       <c r="B17" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136145856</v>
       </c>
       <c r="B18" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136145788</v>
       </c>
       <c r="B19" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136145879</v>
       </c>
       <c r="B20" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136145880</v>
       </c>
       <c r="B21" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136145899</v>
       </c>
       <c r="B22" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136145877</v>
       </c>
       <c r="B23" t="n">
-        <v>91987</v>
+        <v>91988</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136145794</v>
       </c>
       <c r="B24" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136145862</v>
       </c>
       <c r="B25" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136145906</v>
       </c>
       <c r="B26" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>136145909</v>
       </c>
       <c r="B78" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>136145891</v>
       </c>
       <c r="B79" t="n">
-        <v>104014</v>
+        <v>104015</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 34803-2026 artfynd.xlsx
+++ b/artfynd/A 34803-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145878</v>
       </c>
       <c r="B2" t="n">
-        <v>92016</v>
+        <v>92017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145849</v>
       </c>
       <c r="B3" t="n">
-        <v>92461</v>
+        <v>92462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145789</v>
       </c>
       <c r="B4" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145817</v>
       </c>
       <c r="B5" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145828</v>
       </c>
       <c r="B6" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145844</v>
       </c>
       <c r="B7" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136145850</v>
       </c>
       <c r="B8" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136145853</v>
       </c>
       <c r="B9" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136145870</v>
       </c>
       <c r="B10" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136145874</v>
       </c>
       <c r="B11" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136145885</v>
       </c>
       <c r="B12" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136145902</v>
       </c>
       <c r="B13" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136145790</v>
       </c>
       <c r="B14" t="n">
-        <v>79539</v>
+        <v>79540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136145805</v>
       </c>
       <c r="B15" t="n">
-        <v>81426</v>
+        <v>81427</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136145813</v>
       </c>
       <c r="B16" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136145835</v>
       </c>
       <c r="B17" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136145856</v>
       </c>
       <c r="B18" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136145788</v>
       </c>
       <c r="B19" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136145879</v>
       </c>
       <c r="B20" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136145880</v>
       </c>
       <c r="B21" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136145899</v>
       </c>
       <c r="B22" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136145877</v>
       </c>
       <c r="B23" t="n">
-        <v>91988</v>
+        <v>91989</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136145794</v>
       </c>
       <c r="B24" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136145862</v>
       </c>
       <c r="B25" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136145906</v>
       </c>
       <c r="B26" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136145854</v>
       </c>
       <c r="B27" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136145864</v>
       </c>
       <c r="B28" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136145803</v>
       </c>
       <c r="B29" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136145843</v>
       </c>
       <c r="B30" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136145882</v>
       </c>
       <c r="B31" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136145890</v>
       </c>
       <c r="B32" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136145822</v>
       </c>
       <c r="B33" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136145833</v>
       </c>
       <c r="B34" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136145866</v>
       </c>
       <c r="B35" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136145868</v>
       </c>
       <c r="B36" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136145884</v>
       </c>
       <c r="B37" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136145895</v>
       </c>
       <c r="B38" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136145896</v>
       </c>
       <c r="B39" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136145783</v>
       </c>
       <c r="B40" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136145785</v>
       </c>
       <c r="B41" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136145787</v>
       </c>
       <c r="B42" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136145791</v>
       </c>
       <c r="B43" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136145793</v>
       </c>
       <c r="B44" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136145796</v>
       </c>
       <c r="B45" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136145797</v>
       </c>
       <c r="B46" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136145799</v>
       </c>
       <c r="B47" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136145801</v>
       </c>
       <c r="B48" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136145806</v>
       </c>
       <c r="B49" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136145807</v>
       </c>
       <c r="B50" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136145809</v>
       </c>
       <c r="B51" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136145810</v>
       </c>
       <c r="B52" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136145812</v>
       </c>
       <c r="B53" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136145815</v>
       </c>
       <c r="B54" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136145823</v>
       </c>
       <c r="B55" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136145824</v>
       </c>
       <c r="B56" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136145827</v>
       </c>
       <c r="B57" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136145829</v>
       </c>
       <c r="B58" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136145834</v>
       </c>
       <c r="B59" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136145837</v>
       </c>
       <c r="B60" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136145839</v>
       </c>
       <c r="B61" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136145842</v>
       </c>
       <c r="B62" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136145845</v>
       </c>
       <c r="B63" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136145852</v>
       </c>
       <c r="B64" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136145883</v>
       </c>
       <c r="B65" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136145887</v>
       </c>
       <c r="B66" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136145905</v>
       </c>
       <c r="B67" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136145863</v>
       </c>
       <c r="B68" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136145802</v>
       </c>
       <c r="B69" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136145861</v>
       </c>
       <c r="B70" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>136145872</v>
       </c>
       <c r="B71" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>136145786</v>
       </c>
       <c r="B73" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>136145840</v>
       </c>
       <c r="B74" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>136145857</v>
       </c>
       <c r="B75" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>136145888</v>
       </c>
       <c r="B76" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>136145798</v>
       </c>
       <c r="B77" t="n">
-        <v>41612</v>
+        <v>41613</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>136145909</v>
       </c>
       <c r="B78" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>136145891</v>
       </c>
       <c r="B79" t="n">
-        <v>104015</v>
+        <v>104016</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>136145784</v>
       </c>
       <c r="B80" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>136145819</v>
       </c>
       <c r="B81" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>136145826</v>
       </c>
       <c r="B82" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>136145832</v>
       </c>
       <c r="B83" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>136145867</v>
       </c>
       <c r="B84" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>136145886</v>
       </c>
       <c r="B85" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>136145904</v>
       </c>
       <c r="B86" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>136145804</v>
       </c>
       <c r="B87" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>136145811</v>
       </c>
       <c r="B88" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>136145816</v>
       </c>
       <c r="B89" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>136145825</v>
       </c>
       <c r="B90" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>136145830</v>
       </c>
       <c r="B91" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>136145847</v>
       </c>
       <c r="B92" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>136145855</v>
       </c>
       <c r="B93" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>136145859</v>
       </c>
       <c r="B94" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>136145860</v>
       </c>
       <c r="B95" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>136145869</v>
       </c>
       <c r="B96" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>136145871</v>
       </c>
       <c r="B97" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>136145873</v>
       </c>
       <c r="B98" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>136145881</v>
       </c>
       <c r="B99" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>136145892</v>
       </c>
       <c r="B100" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>136145893</v>
       </c>
       <c r="B101" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 34803-2026 artfynd.xlsx
+++ b/artfynd/A 34803-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145878</v>
       </c>
       <c r="B2" t="n">
-        <v>92017</v>
+        <v>92023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145849</v>
       </c>
       <c r="B3" t="n">
-        <v>92462</v>
+        <v>92468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145789</v>
       </c>
       <c r="B4" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145817</v>
       </c>
       <c r="B5" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145828</v>
       </c>
       <c r="B6" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145844</v>
       </c>
       <c r="B7" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136145850</v>
       </c>
       <c r="B8" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136145853</v>
       </c>
       <c r="B9" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136145870</v>
       </c>
       <c r="B10" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136145874</v>
       </c>
       <c r="B11" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136145885</v>
       </c>
       <c r="B12" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136145902</v>
       </c>
       <c r="B13" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136145790</v>
       </c>
       <c r="B14" t="n">
-        <v>79540</v>
+        <v>79544</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136145805</v>
       </c>
       <c r="B15" t="n">
-        <v>81427</v>
+        <v>81431</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136145813</v>
       </c>
       <c r="B16" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136145835</v>
       </c>
       <c r="B17" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136145856</v>
       </c>
       <c r="B18" t="n">
-        <v>91076</v>
+        <v>91082</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136145788</v>
       </c>
       <c r="B19" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136145879</v>
       </c>
       <c r="B20" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136145880</v>
       </c>
       <c r="B21" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136145899</v>
       </c>
       <c r="B22" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136145877</v>
       </c>
       <c r="B23" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136145794</v>
       </c>
       <c r="B24" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136145862</v>
       </c>
       <c r="B25" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136145906</v>
       </c>
       <c r="B26" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136145854</v>
       </c>
       <c r="B27" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136145864</v>
       </c>
       <c r="B28" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136145803</v>
       </c>
       <c r="B29" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136145843</v>
       </c>
       <c r="B30" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136145882</v>
       </c>
       <c r="B31" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136145890</v>
       </c>
       <c r="B32" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136145822</v>
       </c>
       <c r="B33" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136145833</v>
       </c>
       <c r="B34" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136145866</v>
       </c>
       <c r="B35" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136145868</v>
       </c>
       <c r="B36" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136145884</v>
       </c>
       <c r="B37" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136145895</v>
       </c>
       <c r="B38" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136145896</v>
       </c>
       <c r="B39" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136145783</v>
       </c>
       <c r="B40" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136145785</v>
       </c>
       <c r="B41" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136145787</v>
       </c>
       <c r="B42" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136145791</v>
       </c>
       <c r="B43" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136145793</v>
       </c>
       <c r="B44" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136145796</v>
       </c>
       <c r="B45" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136145797</v>
       </c>
       <c r="B46" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136145799</v>
       </c>
       <c r="B47" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136145801</v>
       </c>
       <c r="B48" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136145806</v>
       </c>
       <c r="B49" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136145807</v>
       </c>
       <c r="B50" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136145809</v>
       </c>
       <c r="B51" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136145810</v>
       </c>
       <c r="B52" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136145812</v>
       </c>
       <c r="B53" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136145815</v>
       </c>
       <c r="B54" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136145823</v>
       </c>
       <c r="B55" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136145824</v>
       </c>
       <c r="B56" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136145827</v>
       </c>
       <c r="B57" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136145829</v>
       </c>
       <c r="B58" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136145834</v>
       </c>
       <c r="B59" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136145837</v>
       </c>
       <c r="B60" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136145839</v>
       </c>
       <c r="B61" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136145842</v>
       </c>
       <c r="B62" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136145845</v>
       </c>
       <c r="B63" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136145852</v>
       </c>
       <c r="B64" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136145883</v>
       </c>
       <c r="B65" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136145887</v>
       </c>
       <c r="B66" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136145905</v>
       </c>
       <c r="B67" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136145863</v>
       </c>
       <c r="B68" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136145802</v>
       </c>
       <c r="B69" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136145861</v>
       </c>
       <c r="B70" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>136145872</v>
       </c>
       <c r="B71" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>136145786</v>
       </c>
       <c r="B73" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>136145840</v>
       </c>
       <c r="B74" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>136145857</v>
       </c>
       <c r="B75" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>136145888</v>
       </c>
       <c r="B76" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>136145909</v>
       </c>
       <c r="B78" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>136145891</v>
       </c>
       <c r="B79" t="n">
-        <v>104016</v>
+        <v>104022</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>136145784</v>
       </c>
       <c r="B80" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>136145819</v>
       </c>
       <c r="B81" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>136145826</v>
       </c>
       <c r="B82" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>136145832</v>
       </c>
       <c r="B83" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>136145867</v>
       </c>
       <c r="B84" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>136145886</v>
       </c>
       <c r="B85" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>136145904</v>
       </c>
       <c r="B86" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>136145804</v>
       </c>
       <c r="B87" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>136145811</v>
       </c>
       <c r="B88" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>136145816</v>
       </c>
       <c r="B89" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>136145825</v>
       </c>
       <c r="B90" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>136145830</v>
       </c>
       <c r="B91" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>136145847</v>
       </c>
       <c r="B92" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>136145855</v>
       </c>
       <c r="B93" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>136145859</v>
       </c>
       <c r="B94" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>136145860</v>
       </c>
       <c r="B95" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>136145869</v>
       </c>
       <c r="B96" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>136145871</v>
       </c>
       <c r="B97" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>136145873</v>
       </c>
       <c r="B98" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>136145881</v>
       </c>
       <c r="B99" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>136145892</v>
       </c>
       <c r="B100" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>136145893</v>
       </c>
       <c r="B101" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 34803-2026 artfynd.xlsx
+++ b/artfynd/A 34803-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145878</v>
       </c>
       <c r="B2" t="n">
-        <v>92023</v>
+        <v>92024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145849</v>
       </c>
       <c r="B3" t="n">
-        <v>92468</v>
+        <v>92469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145789</v>
       </c>
       <c r="B4" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145817</v>
       </c>
       <c r="B5" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145828</v>
       </c>
       <c r="B6" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145844</v>
       </c>
       <c r="B7" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136145850</v>
       </c>
       <c r="B8" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136145853</v>
       </c>
       <c r="B9" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136145870</v>
       </c>
       <c r="B10" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136145874</v>
       </c>
       <c r="B11" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136145885</v>
       </c>
       <c r="B12" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136145902</v>
       </c>
       <c r="B13" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136145790</v>
       </c>
       <c r="B14" t="n">
-        <v>79544</v>
+        <v>79545</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136145805</v>
       </c>
       <c r="B15" t="n">
-        <v>81431</v>
+        <v>81432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136145813</v>
       </c>
       <c r="B16" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136145835</v>
       </c>
       <c r="B17" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136145856</v>
       </c>
       <c r="B18" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136145788</v>
       </c>
       <c r="B19" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136145879</v>
       </c>
       <c r="B20" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136145880</v>
       </c>
       <c r="B21" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136145899</v>
       </c>
       <c r="B22" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136145877</v>
       </c>
       <c r="B23" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136145794</v>
       </c>
       <c r="B24" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136145862</v>
       </c>
       <c r="B25" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136145906</v>
       </c>
       <c r="B26" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136145854</v>
       </c>
       <c r="B27" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136145864</v>
       </c>
       <c r="B28" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136145803</v>
       </c>
       <c r="B29" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136145843</v>
       </c>
       <c r="B30" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136145882</v>
       </c>
       <c r="B31" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136145890</v>
       </c>
       <c r="B32" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136145822</v>
       </c>
       <c r="B33" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136145833</v>
       </c>
       <c r="B34" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136145866</v>
       </c>
       <c r="B35" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136145868</v>
       </c>
       <c r="B36" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136145884</v>
       </c>
       <c r="B37" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136145895</v>
       </c>
       <c r="B38" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136145896</v>
       </c>
       <c r="B39" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136145783</v>
       </c>
       <c r="B40" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136145785</v>
       </c>
       <c r="B41" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136145787</v>
       </c>
       <c r="B42" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136145791</v>
       </c>
       <c r="B43" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136145793</v>
       </c>
       <c r="B44" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136145796</v>
       </c>
       <c r="B45" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136145797</v>
       </c>
       <c r="B46" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136145799</v>
       </c>
       <c r="B47" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136145801</v>
       </c>
       <c r="B48" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136145806</v>
       </c>
       <c r="B49" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136145807</v>
       </c>
       <c r="B50" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136145809</v>
       </c>
       <c r="B51" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136145810</v>
       </c>
       <c r="B52" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136145812</v>
       </c>
       <c r="B53" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136145815</v>
       </c>
       <c r="B54" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136145823</v>
       </c>
       <c r="B55" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136145824</v>
       </c>
       <c r="B56" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136145827</v>
       </c>
       <c r="B57" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136145829</v>
       </c>
       <c r="B58" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136145834</v>
       </c>
       <c r="B59" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136145837</v>
       </c>
       <c r="B60" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136145839</v>
       </c>
       <c r="B61" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136145842</v>
       </c>
       <c r="B62" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136145845</v>
       </c>
       <c r="B63" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136145852</v>
       </c>
       <c r="B64" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136145883</v>
       </c>
       <c r="B65" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136145887</v>
       </c>
       <c r="B66" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136145905</v>
       </c>
       <c r="B67" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136145863</v>
       </c>
       <c r="B68" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136145802</v>
       </c>
       <c r="B69" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136145861</v>
       </c>
       <c r="B70" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>136145872</v>
       </c>
       <c r="B71" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>136145786</v>
       </c>
       <c r="B73" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>136145840</v>
       </c>
       <c r="B74" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>136145857</v>
       </c>
       <c r="B75" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>136145888</v>
       </c>
       <c r="B76" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>136145909</v>
       </c>
       <c r="B78" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>136145891</v>
       </c>
       <c r="B79" t="n">
-        <v>104022</v>
+        <v>104023</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>136145784</v>
       </c>
       <c r="B80" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>136145819</v>
       </c>
       <c r="B81" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>136145826</v>
       </c>
       <c r="B82" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>136145832</v>
       </c>
       <c r="B83" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>136145867</v>
       </c>
       <c r="B84" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>136145886</v>
       </c>
       <c r="B85" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>136145904</v>
       </c>
       <c r="B86" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>136145804</v>
       </c>
       <c r="B87" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>136145811</v>
       </c>
       <c r="B88" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>136145816</v>
       </c>
       <c r="B89" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>136145825</v>
       </c>
       <c r="B90" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>136145830</v>
       </c>
       <c r="B91" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>136145847</v>
       </c>
       <c r="B92" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>136145855</v>
       </c>
       <c r="B93" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>136145859</v>
       </c>
       <c r="B94" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>136145860</v>
       </c>
       <c r="B95" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>136145869</v>
       </c>
       <c r="B96" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>136145871</v>
       </c>
       <c r="B97" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>136145873</v>
       </c>
       <c r="B98" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>136145881</v>
       </c>
       <c r="B99" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>136145892</v>
       </c>
       <c r="B100" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>136145893</v>
       </c>
       <c r="B101" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 34803-2026 artfynd.xlsx
+++ b/artfynd/A 34803-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145878</v>
       </c>
       <c r="B2" t="n">
-        <v>92024</v>
+        <v>92030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145849</v>
       </c>
       <c r="B3" t="n">
-        <v>92469</v>
+        <v>92475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145789</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145817</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145828</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145844</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136145850</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136145853</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136145870</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136145874</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136145885</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136145902</v>
       </c>
       <c r="B13" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136145790</v>
       </c>
       <c r="B14" t="n">
-        <v>79545</v>
+        <v>79549</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136145805</v>
       </c>
       <c r="B15" t="n">
-        <v>81432</v>
+        <v>81436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136145813</v>
       </c>
       <c r="B16" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136145835</v>
       </c>
       <c r="B17" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136145856</v>
       </c>
       <c r="B18" t="n">
-        <v>91083</v>
+        <v>91089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136145788</v>
       </c>
       <c r="B19" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136145879</v>
       </c>
       <c r="B20" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136145880</v>
       </c>
       <c r="B21" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136145899</v>
       </c>
       <c r="B22" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136145877</v>
       </c>
       <c r="B23" t="n">
-        <v>91996</v>
+        <v>92002</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136145794</v>
       </c>
       <c r="B24" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136145862</v>
       </c>
       <c r="B25" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136145906</v>
       </c>
       <c r="B26" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136145854</v>
       </c>
       <c r="B27" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136145864</v>
       </c>
       <c r="B28" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136145803</v>
       </c>
       <c r="B29" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136145843</v>
       </c>
       <c r="B30" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136145882</v>
       </c>
       <c r="B31" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136145890</v>
       </c>
       <c r="B32" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136145822</v>
       </c>
       <c r="B33" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136145833</v>
       </c>
       <c r="B34" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136145866</v>
       </c>
       <c r="B35" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136145868</v>
       </c>
       <c r="B36" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136145884</v>
       </c>
       <c r="B37" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136145895</v>
       </c>
       <c r="B38" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136145896</v>
       </c>
       <c r="B39" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136145783</v>
       </c>
       <c r="B40" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136145785</v>
       </c>
       <c r="B41" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136145787</v>
       </c>
       <c r="B42" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136145791</v>
       </c>
       <c r="B43" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136145793</v>
       </c>
       <c r="B44" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136145796</v>
       </c>
       <c r="B45" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136145797</v>
       </c>
       <c r="B46" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136145799</v>
       </c>
       <c r="B47" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136145801</v>
       </c>
       <c r="B48" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136145806</v>
       </c>
       <c r="B49" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136145807</v>
       </c>
       <c r="B50" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136145809</v>
       </c>
       <c r="B51" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136145810</v>
       </c>
       <c r="B52" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136145812</v>
       </c>
       <c r="B53" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136145815</v>
       </c>
       <c r="B54" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136145823</v>
       </c>
       <c r="B55" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136145824</v>
       </c>
       <c r="B56" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136145827</v>
       </c>
       <c r="B57" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136145829</v>
       </c>
       <c r="B58" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136145834</v>
       </c>
       <c r="B59" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136145837</v>
       </c>
       <c r="B60" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136145839</v>
       </c>
       <c r="B61" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136145842</v>
       </c>
       <c r="B62" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136145845</v>
       </c>
       <c r="B63" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136145852</v>
       </c>
       <c r="B64" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136145883</v>
       </c>
       <c r="B65" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136145887</v>
       </c>
       <c r="B66" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136145905</v>
       </c>
       <c r="B67" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136145863</v>
       </c>
       <c r="B68" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136145802</v>
       </c>
       <c r="B69" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>136145909</v>
       </c>
       <c r="B78" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>136145891</v>
       </c>
       <c r="B79" t="n">
-        <v>104023</v>
+        <v>104034</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>136145784</v>
       </c>
       <c r="B80" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>136145819</v>
       </c>
       <c r="B81" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>136145826</v>
       </c>
       <c r="B82" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>136145832</v>
       </c>
       <c r="B83" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>136145867</v>
       </c>
       <c r="B84" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>136145886</v>
       </c>
       <c r="B85" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>136145904</v>
       </c>
       <c r="B86" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>136145804</v>
       </c>
       <c r="B87" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>136145811</v>
       </c>
       <c r="B88" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>136145816</v>
       </c>
       <c r="B89" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>136145825</v>
       </c>
       <c r="B90" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>136145830</v>
       </c>
       <c r="B91" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>136145847</v>
       </c>
       <c r="B92" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>136145855</v>
       </c>
       <c r="B93" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>136145859</v>
       </c>
       <c r="B94" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>136145860</v>
       </c>
       <c r="B95" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>136145869</v>
       </c>
       <c r="B96" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>136145871</v>
       </c>
       <c r="B97" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>136145873</v>
       </c>
       <c r="B98" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>136145881</v>
       </c>
       <c r="B99" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>136145892</v>
       </c>
       <c r="B100" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>136145893</v>
       </c>
       <c r="B101" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 34803-2026 artfynd.xlsx
+++ b/artfynd/A 34803-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145878</v>
       </c>
       <c r="B2" t="n">
-        <v>92030</v>
+        <v>92037</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145849</v>
       </c>
       <c r="B3" t="n">
-        <v>92475</v>
+        <v>92482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145789</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145817</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145828</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145844</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136145850</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136145853</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136145870</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136145874</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136145885</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136145902</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136145790</v>
       </c>
       <c r="B14" t="n">
-        <v>79549</v>
+        <v>79555</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136145805</v>
       </c>
       <c r="B15" t="n">
-        <v>81436</v>
+        <v>81442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136145813</v>
       </c>
       <c r="B16" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136145835</v>
       </c>
       <c r="B17" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136145856</v>
       </c>
       <c r="B18" t="n">
-        <v>91089</v>
+        <v>91096</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136145788</v>
       </c>
       <c r="B19" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136145879</v>
       </c>
       <c r="B20" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136145880</v>
       </c>
       <c r="B21" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136145899</v>
       </c>
       <c r="B22" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136145877</v>
       </c>
       <c r="B23" t="n">
-        <v>92002</v>
+        <v>92009</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136145794</v>
       </c>
       <c r="B24" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136145862</v>
       </c>
       <c r="B25" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136145906</v>
       </c>
       <c r="B26" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136145854</v>
       </c>
       <c r="B27" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136145864</v>
       </c>
       <c r="B28" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136145803</v>
       </c>
       <c r="B29" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136145843</v>
       </c>
       <c r="B30" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136145882</v>
       </c>
       <c r="B31" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136145890</v>
       </c>
       <c r="B32" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136145822</v>
       </c>
       <c r="B33" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136145833</v>
       </c>
       <c r="B34" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136145866</v>
       </c>
       <c r="B35" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136145868</v>
       </c>
       <c r="B36" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136145884</v>
       </c>
       <c r="B37" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136145895</v>
       </c>
       <c r="B38" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136145896</v>
       </c>
       <c r="B39" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136145783</v>
       </c>
       <c r="B40" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136145785</v>
       </c>
       <c r="B41" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136145787</v>
       </c>
       <c r="B42" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136145791</v>
       </c>
       <c r="B43" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136145793</v>
       </c>
       <c r="B44" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136145796</v>
       </c>
       <c r="B45" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136145797</v>
       </c>
       <c r="B46" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136145799</v>
       </c>
       <c r="B47" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136145801</v>
       </c>
       <c r="B48" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136145806</v>
       </c>
       <c r="B49" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136145807</v>
       </c>
       <c r="B50" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136145809</v>
       </c>
       <c r="B51" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136145810</v>
       </c>
       <c r="B52" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136145812</v>
       </c>
       <c r="B53" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136145815</v>
       </c>
       <c r="B54" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136145823</v>
       </c>
       <c r="B55" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136145824</v>
       </c>
       <c r="B56" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136145827</v>
       </c>
       <c r="B57" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136145829</v>
       </c>
       <c r="B58" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136145834</v>
       </c>
       <c r="B59" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136145837</v>
       </c>
       <c r="B60" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136145839</v>
       </c>
       <c r="B61" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136145842</v>
       </c>
       <c r="B62" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136145845</v>
       </c>
       <c r="B63" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136145852</v>
       </c>
       <c r="B64" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136145883</v>
       </c>
       <c r="B65" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136145887</v>
       </c>
       <c r="B66" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136145905</v>
       </c>
       <c r="B67" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136145863</v>
       </c>
       <c r="B68" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136145802</v>
       </c>
       <c r="B69" t="n">
-        <v>78458</v>
+        <v>78464</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136145861</v>
       </c>
       <c r="B70" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>136145872</v>
       </c>
       <c r="B71" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>136145786</v>
       </c>
       <c r="B73" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>136145840</v>
       </c>
       <c r="B74" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>136145857</v>
       </c>
       <c r="B75" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>136145888</v>
       </c>
       <c r="B76" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>136145798</v>
       </c>
       <c r="B77" t="n">
-        <v>41613</v>
+        <v>41618</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>136145909</v>
       </c>
       <c r="B78" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>136145891</v>
       </c>
       <c r="B79" t="n">
-        <v>104034</v>
+        <v>104047</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>136145784</v>
       </c>
       <c r="B80" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>136145819</v>
       </c>
       <c r="B81" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>136145826</v>
       </c>
       <c r="B82" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>136145832</v>
       </c>
       <c r="B83" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>136145867</v>
       </c>
       <c r="B84" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>136145886</v>
       </c>
       <c r="B85" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>136145904</v>
       </c>
       <c r="B86" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>136145804</v>
       </c>
       <c r="B87" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>136145811</v>
       </c>
       <c r="B88" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>136145816</v>
       </c>
       <c r="B89" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>136145825</v>
       </c>
       <c r="B90" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>136145830</v>
       </c>
       <c r="B91" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>136145847</v>
       </c>
       <c r="B92" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>136145855</v>
       </c>
       <c r="B93" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>136145859</v>
       </c>
       <c r="B94" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>136145860</v>
       </c>
       <c r="B95" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>136145869</v>
       </c>
       <c r="B96" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>136145871</v>
       </c>
       <c r="B97" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>136145873</v>
       </c>
       <c r="B98" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>136145881</v>
       </c>
       <c r="B99" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>136145892</v>
       </c>
       <c r="B100" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>136145893</v>
       </c>
       <c r="B101" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 34803-2026 artfynd.xlsx
+++ b/artfynd/A 34803-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145878</v>
       </c>
       <c r="B2" t="n">
-        <v>92037</v>
+        <v>92038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145849</v>
       </c>
       <c r="B3" t="n">
-        <v>92482</v>
+        <v>92483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136145813</v>
       </c>
       <c r="B16" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136145835</v>
       </c>
       <c r="B17" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136145856</v>
       </c>
       <c r="B18" t="n">
-        <v>91096</v>
+        <v>91097</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136145788</v>
       </c>
       <c r="B19" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136145879</v>
       </c>
       <c r="B20" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136145880</v>
       </c>
       <c r="B21" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136145899</v>
       </c>
       <c r="B22" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136145877</v>
       </c>
       <c r="B23" t="n">
-        <v>92009</v>
+        <v>92010</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136145794</v>
       </c>
       <c r="B24" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136145862</v>
       </c>
       <c r="B25" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136145906</v>
       </c>
       <c r="B26" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>136145909</v>
       </c>
       <c r="B78" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>136145891</v>
       </c>
       <c r="B79" t="n">
-        <v>104047</v>
+        <v>104048</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 34803-2026 artfynd.xlsx
+++ b/artfynd/A 34803-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145878</v>
       </c>
       <c r="B2" t="n">
-        <v>92038</v>
+        <v>92051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145849</v>
       </c>
       <c r="B3" t="n">
-        <v>92483</v>
+        <v>92496</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145789</v>
       </c>
       <c r="B4" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145817</v>
       </c>
       <c r="B5" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145828</v>
       </c>
       <c r="B6" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145844</v>
       </c>
       <c r="B7" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136145850</v>
       </c>
       <c r="B8" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136145853</v>
       </c>
       <c r="B9" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136145870</v>
       </c>
       <c r="B10" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136145874</v>
       </c>
       <c r="B11" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136145885</v>
       </c>
       <c r="B12" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136145902</v>
       </c>
       <c r="B13" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136145790</v>
       </c>
       <c r="B14" t="n">
-        <v>79555</v>
+        <v>79568</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136145805</v>
       </c>
       <c r="B15" t="n">
-        <v>81442</v>
+        <v>81455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136145813</v>
       </c>
       <c r="B16" t="n">
-        <v>92267</v>
+        <v>92280</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136145835</v>
       </c>
       <c r="B17" t="n">
-        <v>92267</v>
+        <v>92280</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136145856</v>
       </c>
       <c r="B18" t="n">
-        <v>91097</v>
+        <v>91110</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136145788</v>
       </c>
       <c r="B19" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136145879</v>
       </c>
       <c r="B20" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136145880</v>
       </c>
       <c r="B21" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136145899</v>
       </c>
       <c r="B22" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136145877</v>
       </c>
       <c r="B23" t="n">
-        <v>92010</v>
+        <v>92023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136145794</v>
       </c>
       <c r="B24" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136145862</v>
       </c>
       <c r="B25" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136145906</v>
       </c>
       <c r="B26" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136145854</v>
       </c>
       <c r="B27" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136145864</v>
       </c>
       <c r="B28" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136145803</v>
       </c>
       <c r="B29" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136145843</v>
       </c>
       <c r="B30" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136145882</v>
       </c>
       <c r="B31" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136145890</v>
       </c>
       <c r="B32" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136145822</v>
       </c>
       <c r="B33" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136145833</v>
       </c>
       <c r="B34" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136145866</v>
       </c>
       <c r="B35" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136145868</v>
       </c>
       <c r="B36" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136145884</v>
       </c>
       <c r="B37" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136145895</v>
       </c>
       <c r="B38" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136145896</v>
       </c>
       <c r="B39" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136145783</v>
       </c>
       <c r="B40" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136145785</v>
       </c>
       <c r="B41" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136145787</v>
       </c>
       <c r="B42" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136145791</v>
       </c>
       <c r="B43" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136145793</v>
       </c>
       <c r="B44" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136145796</v>
       </c>
       <c r="B45" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136145797</v>
       </c>
       <c r="B46" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136145799</v>
       </c>
       <c r="B47" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136145801</v>
       </c>
       <c r="B48" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136145806</v>
       </c>
       <c r="B49" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136145807</v>
       </c>
       <c r="B50" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136145809</v>
       </c>
       <c r="B51" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136145810</v>
       </c>
       <c r="B52" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136145812</v>
       </c>
       <c r="B53" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136145815</v>
       </c>
       <c r="B54" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136145823</v>
       </c>
       <c r="B55" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136145824</v>
       </c>
       <c r="B56" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136145827</v>
       </c>
       <c r="B57" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136145829</v>
       </c>
       <c r="B58" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136145834</v>
       </c>
       <c r="B59" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136145837</v>
       </c>
       <c r="B60" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136145839</v>
       </c>
       <c r="B61" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136145842</v>
       </c>
       <c r="B62" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136145845</v>
       </c>
       <c r="B63" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136145852</v>
       </c>
       <c r="B64" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136145883</v>
       </c>
       <c r="B65" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136145887</v>
       </c>
       <c r="B66" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136145905</v>
       </c>
       <c r="B67" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136145863</v>
       </c>
       <c r="B68" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136145802</v>
       </c>
       <c r="B69" t="n">
-        <v>78464</v>
+        <v>78477</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136145861</v>
       </c>
       <c r="B70" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>136145872</v>
       </c>
       <c r="B71" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>136145786</v>
       </c>
       <c r="B73" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>136145840</v>
       </c>
       <c r="B74" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>136145857</v>
       </c>
       <c r="B75" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>136145888</v>
       </c>
       <c r="B76" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>136145798</v>
       </c>
       <c r="B77" t="n">
-        <v>41618</v>
+        <v>41631</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>136145909</v>
       </c>
       <c r="B78" t="n">
-        <v>98196</v>
+        <v>98209</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>136145891</v>
       </c>
       <c r="B79" t="n">
-        <v>104048</v>
+        <v>104061</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>136145784</v>
       </c>
       <c r="B80" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>136145819</v>
       </c>
       <c r="B81" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>136145826</v>
       </c>
       <c r="B82" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>136145832</v>
       </c>
       <c r="B83" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>136145867</v>
       </c>
       <c r="B84" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>136145886</v>
       </c>
       <c r="B85" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>136145904</v>
       </c>
       <c r="B86" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>136145804</v>
       </c>
       <c r="B87" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>136145811</v>
       </c>
       <c r="B88" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>136145816</v>
       </c>
       <c r="B89" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>136145825</v>
       </c>
       <c r="B90" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>136145830</v>
       </c>
       <c r="B91" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>136145847</v>
       </c>
       <c r="B92" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>136145855</v>
       </c>
       <c r="B93" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>136145859</v>
       </c>
       <c r="B94" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>136145860</v>
       </c>
       <c r="B95" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>136145869</v>
       </c>
       <c r="B96" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>136145871</v>
       </c>
       <c r="B97" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>136145873</v>
       </c>
       <c r="B98" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>136145881</v>
       </c>
       <c r="B99" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>136145892</v>
       </c>
       <c r="B100" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>136145893</v>
       </c>
       <c r="B101" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 34803-2026 artfynd.xlsx
+++ b/artfynd/A 34803-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145878</v>
       </c>
       <c r="B2" t="n">
-        <v>92051</v>
+        <v>92052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145849</v>
       </c>
       <c r="B3" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145789</v>
       </c>
       <c r="B4" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145817</v>
       </c>
       <c r="B5" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145828</v>
       </c>
       <c r="B6" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145844</v>
       </c>
       <c r="B7" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136145850</v>
       </c>
       <c r="B8" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136145853</v>
       </c>
       <c r="B9" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136145870</v>
       </c>
       <c r="B10" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136145874</v>
       </c>
       <c r="B11" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136145885</v>
       </c>
       <c r="B12" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136145902</v>
       </c>
       <c r="B13" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136145790</v>
       </c>
       <c r="B14" t="n">
-        <v>79568</v>
+        <v>79569</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136145805</v>
       </c>
       <c r="B15" t="n">
-        <v>81455</v>
+        <v>81456</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136145813</v>
       </c>
       <c r="B16" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136145835</v>
       </c>
       <c r="B17" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136145856</v>
       </c>
       <c r="B18" t="n">
-        <v>91110</v>
+        <v>91111</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136145788</v>
       </c>
       <c r="B19" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136145879</v>
       </c>
       <c r="B20" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136145880</v>
       </c>
       <c r="B21" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136145899</v>
       </c>
       <c r="B22" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136145877</v>
       </c>
       <c r="B23" t="n">
-        <v>92023</v>
+        <v>92024</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136145794</v>
       </c>
       <c r="B24" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136145862</v>
       </c>
       <c r="B25" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136145906</v>
       </c>
       <c r="B26" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136145854</v>
       </c>
       <c r="B27" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136145864</v>
       </c>
       <c r="B28" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136145803</v>
       </c>
       <c r="B29" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136145843</v>
       </c>
       <c r="B30" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136145882</v>
       </c>
       <c r="B31" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136145890</v>
       </c>
       <c r="B32" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136145822</v>
       </c>
       <c r="B33" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136145833</v>
       </c>
       <c r="B34" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136145866</v>
       </c>
       <c r="B35" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136145868</v>
       </c>
       <c r="B36" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136145884</v>
       </c>
       <c r="B37" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136145895</v>
       </c>
       <c r="B38" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136145896</v>
       </c>
       <c r="B39" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136145783</v>
       </c>
       <c r="B40" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136145785</v>
       </c>
       <c r="B41" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136145787</v>
       </c>
       <c r="B42" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136145791</v>
       </c>
       <c r="B43" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136145793</v>
       </c>
       <c r="B44" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136145796</v>
       </c>
       <c r="B45" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136145797</v>
       </c>
       <c r="B46" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136145799</v>
       </c>
       <c r="B47" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136145801</v>
       </c>
       <c r="B48" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136145806</v>
       </c>
       <c r="B49" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136145807</v>
       </c>
       <c r="B50" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136145809</v>
       </c>
       <c r="B51" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136145810</v>
       </c>
       <c r="B52" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136145812</v>
       </c>
       <c r="B53" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136145815</v>
       </c>
       <c r="B54" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136145823</v>
       </c>
       <c r="B55" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136145824</v>
       </c>
       <c r="B56" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136145827</v>
       </c>
       <c r="B57" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136145829</v>
       </c>
       <c r="B58" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136145834</v>
       </c>
       <c r="B59" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136145837</v>
       </c>
       <c r="B60" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136145839</v>
       </c>
       <c r="B61" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136145842</v>
       </c>
       <c r="B62" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136145845</v>
       </c>
       <c r="B63" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136145852</v>
       </c>
       <c r="B64" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136145883</v>
       </c>
       <c r="B65" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136145887</v>
       </c>
       <c r="B66" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136145905</v>
       </c>
       <c r="B67" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136145863</v>
       </c>
       <c r="B68" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136145802</v>
       </c>
       <c r="B69" t="n">
-        <v>78477</v>
+        <v>78478</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>136145909</v>
       </c>
       <c r="B78" t="n">
-        <v>98209</v>
+        <v>98210</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>136145891</v>
       </c>
       <c r="B79" t="n">
-        <v>104061</v>
+        <v>104062</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>136145784</v>
       </c>
       <c r="B80" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>136145819</v>
       </c>
       <c r="B81" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>136145826</v>
       </c>
       <c r="B82" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>136145832</v>
       </c>
       <c r="B83" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>136145867</v>
       </c>
       <c r="B84" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>136145886</v>
       </c>
       <c r="B85" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>136145904</v>
       </c>
       <c r="B86" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>136145804</v>
       </c>
       <c r="B87" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>136145811</v>
       </c>
       <c r="B88" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>136145816</v>
       </c>
       <c r="B89" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>136145825</v>
       </c>
       <c r="B90" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>136145830</v>
       </c>
       <c r="B91" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>136145847</v>
       </c>
       <c r="B92" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>136145855</v>
       </c>
       <c r="B93" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>136145859</v>
       </c>
       <c r="B94" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>136145860</v>
       </c>
       <c r="B95" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>136145869</v>
       </c>
       <c r="B96" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>136145871</v>
       </c>
       <c r="B97" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>136145873</v>
       </c>
       <c r="B98" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>136145881</v>
       </c>
       <c r="B99" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>136145892</v>
       </c>
       <c r="B100" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>136145893</v>
       </c>
       <c r="B101" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
